--- a/Data/EXCEL/Transfer/salemon/202208/5259-salemon-202208.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202208/5259-salemon-202208.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\GoodinfoWebData\salemon\202208\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202208\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FC5F6AFC-C6F4-4FB5-952A-81A63F3022D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7AA9050B-DAAB-4CC6-81D9-1BFDB4D38BFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="1395" windowWidth="22035" windowHeight="12855"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="30645" windowHeight="19905"/>
   </bookViews>
   <sheets>
     <sheet name="5259-salemon-202208" sheetId="2" r:id="rId1"/>
@@ -80,7 +80,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -246,7 +246,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -263,7 +263,7 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -271,13 +271,21 @@
       <sz val="10"/>
       <color rgb="FF008000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -818,7 +826,7 @@
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -827,7 +835,7 @@
     <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -845,22 +853,22 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1221,12 +1229,11 @@
   <dimension ref="A1:Q104"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.875" customWidth="1"/>
-    <col min="2" max="7" width="8.75" customWidth="1"/>
-    <col min="8" max="11" width="10.5" customWidth="1"/>
-    <col min="12" max="12" width="9.125" customWidth="1"/>
-    <col min="13" max="16" width="10.5" customWidth="1"/>
-    <col min="17" max="17" width="10.25" customWidth="1"/>
+    <col min="1" max="1" width="15.625" customWidth="1"/>
+    <col min="2" max="7" width="12.5" customWidth="1"/>
+    <col min="8" max="11" width="15" customWidth="1"/>
+    <col min="12" max="12" width="13.125" customWidth="1"/>
+    <col min="13" max="17" width="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
@@ -6692,7 +6699,7 @@
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="K2:L2"/>
   </mergeCells>
-  <phoneticPr fontId="24" type="noConversion"/>
+  <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>